--- a/calcul de biodéchets.xlsx
+++ b/calcul de biodéchets.xlsx
@@ -8,13 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07826E71-BD5E-4A3C-B7C0-4C300A4CB03E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3FC2446-0409-4E4E-9AEE-8A60E1BD22EF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="5520" windowHeight="40" xr2:uid="{9535F833-AE0D-4C13-995E-BBA90868B46E}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="5520" windowHeight="40" activeTab="1" xr2:uid="{9535F833-AE0D-4C13-995E-BBA90868B46E}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
+    <sheet name="Market peat" sheetId="2" r:id="rId2"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -25,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="80">
   <si>
     <t>Armancourt (60023)</t>
   </si>
@@ -133,6 +138,138 @@
   </si>
   <si>
     <t>Déchets générés par les maisons</t>
+  </si>
+  <si>
+    <t>Qté de tourbe consommé pour le jardinage</t>
+  </si>
+  <si>
+    <t>m3/an</t>
+  </si>
+  <si>
+    <t>Densité</t>
+  </si>
+  <si>
+    <t>kg/m3</t>
+  </si>
+  <si>
+    <t>kg/an</t>
+  </si>
+  <si>
+    <t>Qté de C dans les tourbes</t>
+  </si>
+  <si>
+    <t>kgC/kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C dans les tourbes consommées en france </t>
+  </si>
+  <si>
+    <t>kgC/an</t>
+  </si>
+  <si>
+    <t>Pop en France</t>
+  </si>
+  <si>
+    <t>Consommation de C tourbe par hab</t>
+  </si>
+  <si>
+    <t>kgC/hab</t>
+  </si>
+  <si>
+    <t>Qté de tourbe consommé par hab</t>
+  </si>
+  <si>
+    <t>kg/an/hab</t>
+  </si>
+  <si>
+    <t>C (kg)</t>
+  </si>
+  <si>
+    <t>Tourbe max(kg)</t>
+  </si>
+  <si>
+    <t>Production de tourbe par HC</t>
+  </si>
+  <si>
+    <t>kg/t</t>
+  </si>
+  <si>
+    <t>Tourbe qui peut être substituée (kg)</t>
+  </si>
+  <si>
+    <t>tourbe max/t de déchets</t>
+  </si>
+  <si>
+    <t>tourbe max vendue dans l'arc</t>
+  </si>
+  <si>
+    <t>tourbe max par tonne de déchets</t>
+  </si>
+  <si>
+    <t>kg tourbe/tonne de déchets</t>
+  </si>
+  <si>
+    <t>Nbre de communes en France</t>
+  </si>
+  <si>
+    <t>co2</t>
+  </si>
+  <si>
+    <t>eq</t>
+  </si>
+  <si>
+    <t>hh</t>
+  </si>
+  <si>
+    <t>Pop hab en maison</t>
+  </si>
+  <si>
+    <t>Market_hobby_ARC</t>
+  </si>
+  <si>
+    <t>kg/hab/an</t>
+  </si>
+  <si>
+    <t>Market_pro_ARC</t>
+  </si>
+  <si>
+    <t>Qthé de tourbe par hab</t>
+  </si>
+  <si>
+    <t>Pro_market</t>
+  </si>
+  <si>
+    <t>marché de N en France</t>
+  </si>
+  <si>
+    <t>N par hab</t>
+  </si>
+  <si>
+    <t>Marché de N dans l'ARC</t>
+  </si>
+  <si>
+    <t>kT/an</t>
+  </si>
+  <si>
+    <t>kT/hab/an</t>
+  </si>
+  <si>
+    <t>marché de P en France</t>
+  </si>
+  <si>
+    <t>P/hab</t>
+  </si>
+  <si>
+    <t>Marché de P dans l'ARC</t>
+  </si>
+  <si>
+    <t>marché de K en France</t>
+  </si>
+  <si>
+    <t>K/hab</t>
+  </si>
+  <si>
+    <t>Marché de K dans l'ARC</t>
   </si>
 </sst>
 </file>
@@ -142,7 +279,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -153,6 +290,13 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -213,7 +357,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="2" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -224,13 +368,32 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="2" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 3" xfId="2" xr:uid="{C44DA8DB-F992-4C59-9122-73E39874C955}"/>
     <cellStyle name="Pourcentage" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -241,6 +404,167 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="mun"/>
+      <sheetName val="waste_gen"/>
+      <sheetName val="tech_pot"/>
+      <sheetName val="dist_market"/>
+      <sheetName val="market"/>
+      <sheetName val="dist_col"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="2">
+          <cell r="B2">
+            <v>755.47870232939465</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>134.53622608695653</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="B4">
+            <v>156.99056470588235</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="B5">
+            <v>43.83239785330948</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="B6">
+            <v>113.91003428331933</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="B7">
+            <v>68.797540238887805</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="B8">
+            <v>145.23549140271493</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="B9">
+            <v>126.52593464788731</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="B10">
+            <v>47.072259332023577</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="B11">
+            <v>29.063999999999997</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="B12">
+            <v>179.2884425556858</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="B13">
+            <v>95.116624345549738</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="B14">
+            <v>37.915901369863015</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="B15">
+            <v>39.790797101449272</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="B16">
+            <v>40.11461895261845</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="B17">
+            <v>264.31269544072944</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="B18">
+            <v>30.935915789473682</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="B19">
+            <v>19.042357142857139</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="B20">
+            <v>49.315776168652619</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="B21">
+            <v>31</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="B22">
+            <v>123.86145497136906</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="B23">
+            <v>50.381951188589539</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Feuil1"/>
+      <sheetName val="Feuil2"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="26">
+          <cell r="C26">
+            <v>1.4284515611925735E-2</v>
+          </cell>
+          <cell r="E26">
+            <v>8.2740684822632665E-3</v>
+          </cell>
+          <cell r="F26">
+            <v>4.4209285281899682E-8</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -544,13 +868,17 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="29.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.08984375" customWidth="1"/>
+    <col min="2" max="2" width="21" customWidth="1"/>
+    <col min="4" max="4" width="21.7265625" customWidth="1"/>
     <col min="5" max="5" width="25.26953125" customWidth="1"/>
     <col min="6" max="6" width="10.90625" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
     <col min="8" max="9" width="10.90625" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="18" width="10.90625" customWidth="1"/>
+    <col min="11" max="12" width="10.90625" customWidth="1"/>
+    <col min="13" max="13" width="15.36328125" customWidth="1"/>
+    <col min="14" max="14" width="18.90625" customWidth="1"/>
+    <col min="15" max="18" width="10.90625" customWidth="1"/>
     <col min="19" max="19" width="28.7265625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="24.90625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="10.90625" customWidth="1"/>
@@ -1763,6 +2091,12 @@
         <v>1.6180488114104619</v>
       </c>
     </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="B25">
+        <f>SUM(B2:B23)</f>
+        <v>85081</v>
+      </c>
+    </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>30</v>
@@ -1785,4 +2119,892 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2B2418B-0A16-4779-A03C-070F8BD637D3}">
+  <dimension ref="A1:V27"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="29.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.81640625" customWidth="1"/>
+    <col min="3" max="4" width="0" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="18.81640625" customWidth="1"/>
+    <col min="9" max="9" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="38.26953125" customWidth="1"/>
+    <col min="12" max="12" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="26.453125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.36328125" customWidth="1"/>
+    <col min="17" max="17" width="15.81640625" customWidth="1"/>
+    <col min="21" max="21" width="11.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" t="s">
+        <v>54</v>
+      </c>
+      <c r="I1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1">
+        <v>757800</v>
+      </c>
+      <c r="M1" t="s">
+        <v>37</v>
+      </c>
+      <c r="N1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O1">
+        <f>69100000</f>
+        <v>69100000</v>
+      </c>
+      <c r="Q1">
+        <f>1670000*0.45</f>
+        <v>751500</v>
+      </c>
+      <c r="R1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T1" t="s">
+        <v>69</v>
+      </c>
+      <c r="U1">
+        <v>1831</v>
+      </c>
+      <c r="V1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <f>$L$4*Feuil1!P2</f>
+        <v>1119.6243862228655</v>
+      </c>
+      <c r="C2">
+        <f>$L$7*Feuil1!B2</f>
+        <v>271.89521838494937</v>
+      </c>
+      <c r="E2">
+        <f>L8*[1]waste_gen!$B$5</f>
+        <v>19212.252292171655</v>
+      </c>
+      <c r="F2">
+        <f>I2/G2</f>
+        <v>438.31168800000006</v>
+      </c>
+      <c r="G2">
+        <f>B2/E2</f>
+        <v>5.8276581485403177E-2</v>
+      </c>
+      <c r="I2">
+        <f>B2/[1]waste_gen!$B$5</f>
+        <v>25.543306801736616</v>
+      </c>
+      <c r="K2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L2">
+        <v>200</v>
+      </c>
+      <c r="M2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2" t="s">
+        <v>59</v>
+      </c>
+      <c r="O2">
+        <v>36529</v>
+      </c>
+      <c r="T2" t="s">
+        <v>70</v>
+      </c>
+      <c r="U2">
+        <f>U1/O1</f>
+        <v>2.6497829232995658E-5</v>
+      </c>
+      <c r="V2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <f>$L$4*Feuil1!P3</f>
+        <v>2102.0806117510856</v>
+      </c>
+      <c r="C3">
+        <f>$L$7*Feuil1!B3</f>
+        <v>495.15086281910277</v>
+      </c>
+      <c r="E3">
+        <f>L8*[1]waste_gen!$B$10</f>
+        <v>20632.321445793008</v>
+      </c>
+      <c r="G3">
+        <f t="shared" ref="G3:G23" si="0">B3/E3</f>
+        <v>0.10188289365662757</v>
+      </c>
+      <c r="I3">
+        <f>B3/[1]waste_gen!$B$10</f>
+        <v>44.656463096960927</v>
+      </c>
+      <c r="K3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L3">
+        <f>L1*L2</f>
+        <v>151560000</v>
+      </c>
+      <c r="M3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N3" t="s">
+        <v>63</v>
+      </c>
+      <c r="O3" s="12">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="P3" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q3">
+        <f>Q1*L2</f>
+        <v>150300000</v>
+      </c>
+      <c r="R3" t="s">
+        <v>40</v>
+      </c>
+      <c r="T3" t="s">
+        <v>74</v>
+      </c>
+      <c r="U3">
+        <v>316</v>
+      </c>
+      <c r="V3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <f>$L$4*Feuil1!P4</f>
+        <v>5185.1443998842251</v>
+      </c>
+      <c r="C4">
+        <f>$L$7*Feuil1!B4</f>
+        <v>1554.0343877279306</v>
+      </c>
+      <c r="E4">
+        <f>[1]waste_gen!$B$9*L8</f>
+        <v>55457.795991293176</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="0"/>
+        <v>9.349712348284249E-2</v>
+      </c>
+      <c r="I4">
+        <f>+B4/[1]waste_gen!$B$9</f>
+        <v>40.980882016909135</v>
+      </c>
+      <c r="K4" t="s">
+        <v>48</v>
+      </c>
+      <c r="L4">
+        <f>L3/O1</f>
+        <v>2.193342981186686</v>
+      </c>
+      <c r="M4" t="s">
+        <v>49</v>
+      </c>
+      <c r="P4" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q4">
+        <f>+Q3/O1</f>
+        <v>2.1751085383502171</v>
+      </c>
+      <c r="R4" t="s">
+        <v>65</v>
+      </c>
+      <c r="T4" t="s">
+        <v>75</v>
+      </c>
+      <c r="U4">
+        <f>U3/O1</f>
+        <v>4.5730824891461646E-6</v>
+      </c>
+      <c r="V4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <f>$L$4*Feuil1!P5</f>
+        <v>981.70873424023159</v>
+      </c>
+      <c r="C5">
+        <f>$L$7*Feuil1!B5</f>
+        <v>224.71483165267728</v>
+      </c>
+      <c r="E5">
+        <f>L8*[1]waste_gen!$B$11</f>
+        <v>12739.090900031999</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="0"/>
+        <v>7.7062699524168221E-2</v>
+      </c>
+      <c r="I5">
+        <f>+B5/[1]waste_gen!$B$11</f>
+        <v>33.777481910274972</v>
+      </c>
+      <c r="K5" t="s">
+        <v>41</v>
+      </c>
+      <c r="L5">
+        <v>0.22176000000000001</v>
+      </c>
+      <c r="M5" t="s">
+        <v>42</v>
+      </c>
+      <c r="T5" t="s">
+        <v>77</v>
+      </c>
+      <c r="U5">
+        <v>354</v>
+      </c>
+      <c r="V5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <f>$L$4*Feuil1!P6</f>
+        <v>6299.2415617945007</v>
+      </c>
+      <c r="C6">
+        <f>$L$7*Feuil1!B6</f>
+        <v>1659.5822632011577</v>
+      </c>
+      <c r="E6">
+        <f>L8*[1]waste_gen!$B$12</f>
+        <v>78584.219895473681</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>8.0159115534559455E-2</v>
+      </c>
+      <c r="I6">
+        <f>+B6/[1]waste_gen!$B$12</f>
+        <v>35.13467723853978</v>
+      </c>
+      <c r="K6" t="s">
+        <v>43</v>
+      </c>
+      <c r="L6">
+        <f>L3*L5</f>
+        <v>33609945.600000001</v>
+      </c>
+      <c r="M6" t="s">
+        <v>44</v>
+      </c>
+      <c r="T6" t="s">
+        <v>78</v>
+      </c>
+      <c r="U6">
+        <f>U5/O1</f>
+        <v>5.1230101302460199E-6</v>
+      </c>
+      <c r="V6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <f>$L$4*Feuil1!P7</f>
+        <v>4386.8329163531116</v>
+      </c>
+      <c r="C7">
+        <f>$L$7*Feuil1!B7</f>
+        <v>1114.8190349522431</v>
+      </c>
+      <c r="E7">
+        <f>L8*[1]waste_gen!$B$13</f>
+        <v>41690.728173759802</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>0.10522322608685425</v>
+      </c>
+      <c r="I7">
+        <f>B7/[1]waste_gen!$B$13</f>
+        <v>46.120569842934721</v>
+      </c>
+      <c r="K7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L7">
+        <f>L6/O1</f>
+        <v>0.4863957395079595</v>
+      </c>
+      <c r="M7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <f>$L$4*Feuil1!P8</f>
+        <v>23341.298068654123</v>
+      </c>
+      <c r="C8">
+        <f>$L$7*Feuil1!B8</f>
+        <v>20170.831317395081</v>
+      </c>
+      <c r="E8">
+        <f>L8*[1]waste_gen!$B$2</f>
+        <v>331135.14526604651</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>7.0488736705675986E-2</v>
+      </c>
+      <c r="I8">
+        <f>B8/[1]waste_gen!$B$2</f>
+        <v>30.896037170452402</v>
+      </c>
+      <c r="K8" t="s">
+        <v>52</v>
+      </c>
+      <c r="L8">
+        <v>438.311688</v>
+      </c>
+      <c r="M8" t="s">
+        <v>53</v>
+      </c>
+      <c r="N8">
+        <f>L3*0.1</f>
+        <v>15156000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <f>$L$4*Feuil1!P9</f>
+        <v>1332.6295738350218</v>
+      </c>
+      <c r="C9">
+        <f>$L$7*Feuil1!B9</f>
+        <v>319.56200085672941</v>
+      </c>
+      <c r="E9">
+        <f>L8*[1]waste_gen!$B$14</f>
+        <v>16618.982731466171</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>8.0187192884666636E-2</v>
+      </c>
+      <c r="I9">
+        <f>B9/[1]waste_gen!$B$14</f>
+        <v>35.14698386925982</v>
+      </c>
+      <c r="M9">
+        <v>438.31168830000001</v>
+      </c>
+      <c r="P9" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q9" s="11">
+        <f>Q5*([2]Feuil1!$C$26 + 0.7318)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <f>$L$4*Feuil1!P10</f>
+        <v>4343.0533517800295</v>
+      </c>
+      <c r="C10">
+        <f>$L$7*Feuil1!B10</f>
+        <v>1141.0844048856729</v>
+      </c>
+      <c r="E10">
+        <f>L8*[1]waste_gen!$B$4</f>
+        <v>68810.79941630851</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="0"/>
+        <v>6.3115868273878883E-2</v>
+      </c>
+      <c r="I10">
+        <f>B10/[1]waste_gen!$B$4</f>
+        <v>27.664422762709496</v>
+      </c>
+      <c r="P10" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q10">
+        <f>Q5*([2]Feuil1!$E$26+(0.7318*0.1685))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <f>$L$4*Feuil1!P11</f>
+        <v>1321.8949146164978</v>
+      </c>
+      <c r="C11">
+        <f>$L$7*Feuil1!B11</f>
+        <v>302.05175423444285</v>
+      </c>
+      <c r="E11">
+        <f>[1]waste_gen!$B$15*L8</f>
+        <v>17440.771444401737</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="0"/>
+        <v>7.5793374096465735E-2</v>
+      </c>
+      <c r="I11">
+        <f>B11/[1]waste_gen!$B$15</f>
+        <v>33.221121739437365</v>
+      </c>
+      <c r="K11" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="L11" s="13">
+        <f>L4*Feuil1!B25</f>
+        <v>186611.81418234445</v>
+      </c>
+      <c r="M11" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="P11" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q11" s="11">
+        <f>Q5*[2]Feuil1!$F$26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <f>$L$4*Feuil1!P12</f>
+        <v>1680.0967755716354</v>
+      </c>
+      <c r="C12">
+        <f>$L$7*Feuil1!B12</f>
+        <v>390.08938308538353</v>
+      </c>
+      <c r="E12">
+        <f>L8*[1]waste_gen!$B$16</f>
+        <v>17582.706346598985</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="0"/>
+        <v>9.5553934784141786E-2</v>
+      </c>
+      <c r="I12">
+        <f>B12/[1]waste_gen!$B$16</f>
+        <v>41.882406450279106</v>
+      </c>
+      <c r="K12" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="L12" s="13">
+        <f>Q4*Feuil1!B25</f>
+        <v>185060.40955137482</v>
+      </c>
+      <c r="M12" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <f>$L$4*Feuil1!P13</f>
+        <v>8562.5438493777147</v>
+      </c>
+      <c r="C13">
+        <f>$L$7*Feuil1!B13</f>
+        <v>2484.0230416671493</v>
+      </c>
+      <c r="E13">
+        <f>L8*[1]waste_gen!$B$7</f>
+        <v>30154.765992354838</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="0"/>
+        <v>0.28395325142130379</v>
+      </c>
+      <c r="I13">
+        <f>B13/[1]waste_gen!$B$7</f>
+        <v>124.46002894356006</v>
+      </c>
+      <c r="K13" t="s">
+        <v>71</v>
+      </c>
+      <c r="L13">
+        <f>U2*Feuil1!B25</f>
+        <v>2.2544618089725037</v>
+      </c>
+      <c r="M13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <f>$L$4*Feuil1!P14</f>
+        <v>9571.9838962662798</v>
+      </c>
+      <c r="C14">
+        <f>$L$7*Feuil1!B14</f>
+        <v>4320.6533540492046</v>
+      </c>
+      <c r="E14">
+        <f>L8*[1]waste_gen!$B$17</f>
+        <v>115851.34369845602</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="0"/>
+        <v>8.2622985549315187E-2</v>
+      </c>
+      <c r="I14">
+        <f>B14/[1]waste_gen!$B$17</f>
+        <v>36.214620263719951</v>
+      </c>
+      <c r="K14" t="s">
+        <v>76</v>
+      </c>
+      <c r="L14">
+        <f>U4*Feuil1!B25</f>
+        <v>0.38908243125904485</v>
+      </c>
+      <c r="M14" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <f>$L$4*Feuil1!P15</f>
+        <v>4550.5896580028939</v>
+      </c>
+      <c r="C15">
+        <f>$L$7*Feuil1!B15</f>
+        <v>1160.5402344659913</v>
+      </c>
+      <c r="E15">
+        <f>L8*[1]waste_gen!$B$6</f>
+        <v>49928.099406859568</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>9.1142857670598473E-2</v>
+      </c>
+      <c r="I15">
+        <f>B15/[1]waste_gen!$B$6</f>
+        <v>39.948979794743764</v>
+      </c>
+      <c r="K15" t="s">
+        <v>79</v>
+      </c>
+      <c r="L15">
+        <f>U6*Feuil1!B25</f>
+        <v>0.43587082489146162</v>
+      </c>
+      <c r="M15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.35">
+      <c r="A16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16">
+        <f>$L$4*Feuil1!P16</f>
+        <v>1410.071689146165</v>
+      </c>
+      <c r="C16">
+        <f>$L$7*Feuil1!B16</f>
+        <v>323.45316677279305</v>
+      </c>
+      <c r="E16">
+        <f>L8*[1]waste_gen!$B$18</f>
+        <v>13559.573469510062</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>0.10399085873289746</v>
+      </c>
+      <c r="I16">
+        <f>B16/[1]waste_gen!$B$18</f>
+        <v>45.580408827785824</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <f>$L$4*Feuil1!P17</f>
+        <v>2226.5953767872652</v>
+      </c>
+      <c r="C17">
+        <f>$L$7*Feuil1!B17</f>
+        <v>530.65775180318383</v>
+      </c>
+      <c r="E17">
+        <f>[1]waste_gen!$B$20*L8</f>
+        <v>21615.681097512301</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="0"/>
+        <v>0.10300833763889675</v>
+      </c>
+      <c r="I17">
+        <f>B17/[1]waste_gen!$B$20</f>
+        <v>45.149758348578764</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18">
+        <f>$L$4*Feuil1!P18</f>
+        <v>701.67586246020255</v>
+      </c>
+      <c r="C18">
+        <f>$L$7*Feuil1!B18</f>
+        <v>163.42896847467441</v>
+      </c>
+      <c r="E18">
+        <f>[1]waste_gen!$B$19*L8</f>
+        <v>8346.4877027845705</v>
+      </c>
+      <c r="G18">
+        <f t="shared" si="0"/>
+        <v>8.4068399480910772E-2</v>
+      </c>
+      <c r="I18">
+        <f>B18/[1]waste_gen!$B$19</f>
+        <v>36.84816208393633</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19">
+        <f>$L$4*Feuil1!P19</f>
+        <v>3779.8563917800288</v>
+      </c>
+      <c r="C19">
+        <f>$L$7*Feuil1!B19</f>
+        <v>859.94766745007234</v>
+      </c>
+      <c r="E19">
+        <f>[1]waste_gen!$B$8*L8</f>
+        <v>63658.413394233467</v>
+      </c>
+      <c r="G19">
+        <f t="shared" si="0"/>
+        <v>5.9377169336149831E-2</v>
+      </c>
+      <c r="I19">
+        <f>B19/[1]waste_gen!$B$8</f>
+        <v>26.025707320389671</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20">
+        <f>$L$4*Feuil1!P20</f>
+        <v>1403.7395079594789</v>
+      </c>
+      <c r="C20">
+        <f>$L$7*Feuil1!B20</f>
+        <v>311.29327328509407</v>
+      </c>
+      <c r="E20">
+        <f>[1]waste_gen!$B$21*L8</f>
+        <v>13587.662328</v>
+      </c>
+      <c r="G20">
+        <f t="shared" si="0"/>
+        <v>0.10330986111325439</v>
+      </c>
+      <c r="I20">
+        <f>B20/[1]waste_gen!$B$21</f>
+        <v>45.281919611596095</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21">
+        <f>$L$4*Feuil1!P21</f>
+        <v>4597.6004554558613</v>
+      </c>
+      <c r="C21">
+        <f>$L$7*Feuil1!B21</f>
+        <v>1409.5748530940666</v>
+      </c>
+      <c r="E21">
+        <f>[1]waste_gen!$B$3*L8</f>
+        <v>58968.800353323553</v>
+      </c>
+      <c r="G21">
+        <f t="shared" si="0"/>
+        <v>7.7966660808909183E-2</v>
+      </c>
+      <c r="I21">
+        <f>B21/[1]waste_gen!$B$3</f>
+        <v>34.173698706876429</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22">
+        <f>$L$4*Feuil1!P22</f>
+        <v>5493.4665707670038</v>
+      </c>
+      <c r="C22">
+        <f>$L$7*Feuil1!B22</f>
+        <v>1868.7324311895804</v>
+      </c>
+      <c r="E22">
+        <f>[1]waste_gen!$B$22*L8</f>
+        <v>54289.923406636764</v>
+      </c>
+      <c r="G22">
+        <f t="shared" si="0"/>
+        <v>0.10118759110452982</v>
+      </c>
+      <c r="I22">
+        <f>B22/[1]waste_gen!$B$22</f>
+        <v>44.351703861680257</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23">
+        <f>$L$4*Feuil1!P23</f>
+        <v>1340.934447698987</v>
+      </c>
+      <c r="C23">
+        <f>$L$7*Feuil1!B23</f>
+        <v>306.91571162952243</v>
+      </c>
+      <c r="E23">
+        <f>[1]waste_gen!$B$23*L8</f>
+        <v>22082.998070204289</v>
+      </c>
+      <c r="G23">
+        <f t="shared" si="0"/>
+        <v>6.072248176791975E-2</v>
+      </c>
+      <c r="I23">
+        <f>B23/[1]waste_gen!$B$23</f>
+        <v>26.615373483246135</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B25">
+        <f>SUM(B2:B23)</f>
+        <v>95732.663000405228</v>
+      </c>
+      <c r="E25">
+        <f>E2/[1]waste_gen!$B$5</f>
+        <v>438.311688</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26">
+        <f>B25/SUM(Feuil1!S2:S23)</f>
+        <v>37.069480446874223</v>
+      </c>
+      <c r="E26" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B27">
+        <f>B26/L8</f>
+        <v>8.4573333227824454E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I23">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>I2=MAX($I$2:$I$23)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>I2=MIN($I$2:$I$23)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="597" r:id="rId1"/>
+</worksheet>
 </file>
--- a/calcul de biodéchets.xlsx
+++ b/calcul de biodéchets.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\hravoaha\Desktop\Thèse\Thèse 2023\Objectif 2\biowaste_optim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3FC2446-0409-4E4E-9AEE-8A60E1BD22EF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{439DE397-0C51-4165-9C3B-B55BBC9D1D85}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="5520" windowHeight="40" activeTab="1" xr2:uid="{9535F833-AE0D-4C13-995E-BBA90868B46E}"/>
   </bookViews>
@@ -2616,6 +2616,10 @@
       <c r="M11" s="13" t="s">
         <v>40</v>
       </c>
+      <c r="N11">
+        <f>L11/L2</f>
+        <v>933.05907091172219</v>
+      </c>
       <c r="P11" t="s">
         <v>62</v>
       </c>
@@ -2657,6 +2661,10 @@
       </c>
       <c r="M12" s="13" t="s">
         <v>40</v>
+      </c>
+      <c r="N12">
+        <f>L12/L2</f>
+        <v>925.30204775687412</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.35">
